--- a/Original experimental data.xlsx
+++ b/Original experimental data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20383"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHD_Thesis\第2章  室内基本力学试验\paper\NC\Recised draft\二审意见\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SynologyDrive\同步工作库\A-博士论文\更新github数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B64B114-1AD7-4B8F-96A0-05998B82D294}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A56698F-5A0D-4435-8F7E-4F1EE12F8B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" xr2:uid="{9FA6F14C-C309-4DBA-81DD-D5334513A472}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9FA6F14C-C309-4DBA-81DD-D5334513A472}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,15 +74,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -102,9 +99,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -142,7 +139,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -248,7 +245,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -390,7 +387,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -399,12 +396,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6DC395-D23C-4FB4-873E-0A1FF853D569}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="8.88671875" style="2"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>5</v>
       </c>
@@ -421,7 +415,7 @@
         <v>19.13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -438,7 +432,7 @@
         <v>20.63</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -455,7 +449,7 @@
         <v>20.91</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -472,7 +466,7 @@
         <v>10.76</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -489,7 +483,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -506,7 +500,7 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -523,7 +517,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -540,7 +534,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -557,7 +551,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -574,7 +568,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -591,7 +585,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -608,7 +602,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -625,7 +619,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -642,7 +636,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -659,7 +653,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>10</v>
       </c>
@@ -673,10 +667,10 @@
         <v>23.65</v>
       </c>
       <c r="E16" s="1">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -693,7 +687,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>10</v>
       </c>
@@ -710,7 +704,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>20</v>
       </c>
@@ -727,7 +721,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -744,7 +738,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -761,7 +755,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -778,7 +772,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -795,7 +789,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -812,7 +806,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -829,7 +823,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>20</v>
       </c>
@@ -846,7 +840,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>20</v>
       </c>
